--- a/r4-ELGA-e-Medikation-uc_5_6/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-uc_5_6/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18933" uniqueCount="1367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18933" uniqueCount="1368">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T08:56:46+00:00</t>
+    <t>2026-07-14T09:07:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3656,13 +3656,16 @@
 </t>
   </si>
   <si>
+    <t>Im Falle einer Fremdmedikation Angabe einer Referenz auf: (Patient | Practitioner | PractitionerRole | RelatedPerson | Organization). Keine Verwendung im Medikationsplan.</t>
+  </si>
+  <si>
     <t>MedicationRequest.reported[x]:reportedBoolean</t>
   </si>
   <si>
     <t>reportedBoolean</t>
   </si>
   <si>
-    <t>Quelle der Information. Mögliche Ausprägungen: [ true | false ]. Bedeutung: false: Verordnung durch den Planeintrag erstellenden GDA | true: Fremdmedikation oder Eigenmedikation des Patienten.</t>
+    <t>Quelle der Information. Bedeutung: false: Verordnung durch den Planeintrag erstellenden GDA | true: Fremdmedikation oder Eigenmedikation des Patienten.</t>
   </si>
   <si>
     <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
@@ -5823,7 +5826,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="179">
@@ -5831,7 +5834,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="180">
@@ -5847,7 +5850,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="182">
@@ -5855,7 +5858,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="183">
@@ -5917,7 +5920,7 @@
         <v>24</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="191">
@@ -5953,7 +5956,7 @@
         <v>32</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="196">
@@ -5961,7 +5964,7 @@
         <v>34</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="197">
@@ -5993,7 +5996,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="201">
@@ -6001,7 +6004,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="202">
@@ -6017,7 +6020,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="204">
@@ -6025,7 +6028,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="205">
@@ -6087,7 +6090,7 @@
         <v>24</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="213">
@@ -6123,7 +6126,7 @@
         <v>32</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="218">
@@ -6131,7 +6134,7 @@
         <v>34</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="219">
@@ -54606,7 +54609,7 @@
         <v>1150</v>
       </c>
       <c r="M464" t="s" s="2">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="N464" t="s" s="2">
         <v>966</v>
@@ -54680,13 +54683,13 @@
         <v>1119</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C465" t="s" s="2">
         <v>963</v>
       </c>
       <c r="D465" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E465" t="s" s="2">
         <v>23</v>
@@ -54711,7 +54714,7 @@
         <v>385</v>
       </c>
       <c r="M465" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="N465" t="s" s="2">
         <v>966</v>
@@ -54814,7 +54817,7 @@
         <v>782</v>
       </c>
       <c r="M466" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="N466" t="s" s="2">
         <v>969</v>
@@ -54919,7 +54922,7 @@
         <v>568</v>
       </c>
       <c r="M467" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="N467" t="s" s="2">
         <v>973</v>
@@ -55024,7 +55027,7 @@
         <v>574</v>
       </c>
       <c r="M468" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="N468" t="s" s="2">
         <v>977</v>
@@ -55129,7 +55132,7 @@
         <v>795</v>
       </c>
       <c r="M469" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="N469" t="s" s="2">
         <v>981</v>
@@ -55232,7 +55235,7 @@
         <v>578</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="N470" t="s" s="2">
         <v>984</v>
@@ -55335,7 +55338,7 @@
         <v>811</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="N471" t="s" s="2">
         <v>987</v>
@@ -55438,7 +55441,7 @@
         <v>989</v>
       </c>
       <c r="M472" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="N472" t="s" s="2">
         <v>991</v>
@@ -55541,7 +55544,7 @@
         <v>367</v>
       </c>
       <c r="M473" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="N473" t="s" s="2">
         <v>993</v>
@@ -55646,7 +55649,7 @@
         <v>881</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="N474" t="s" s="2">
         <v>999</v>
@@ -55749,7 +55752,7 @@
         <v>367</v>
       </c>
       <c r="M475" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="N475" t="s" s="2">
         <v>1002</v>
@@ -55959,7 +55962,7 @@
         <v>1012</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="N477" t="s" s="2">
         <v>1014</v>
@@ -56062,7 +56065,7 @@
         <v>97</v>
       </c>
       <c r="M478" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="N478" t="s" s="2">
         <v>1017</v>
@@ -56162,10 +56165,10 @@
         <v>84</v>
       </c>
       <c r="L479" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="M479" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="N479" t="s" s="2">
         <v>1020</v>
@@ -56268,7 +56271,7 @@
         <v>112</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="N480" t="s" s="2">
         <v>1023</v>
@@ -56373,7 +56376,7 @@
         <v>367</v>
       </c>
       <c r="M481" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="N481" t="s" s="2">
         <v>1027</v>
@@ -56478,7 +56481,7 @@
         <v>1032</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="N482" t="s" s="2">
         <v>1034</v>
@@ -56581,7 +56584,7 @@
         <v>598</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="N483" t="s" s="2">
         <v>1037</v>
@@ -56684,7 +56687,7 @@
         <v>1039</v>
       </c>
       <c r="M484" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="N484" t="s" s="2">
         <v>859</v>
@@ -56789,7 +56792,7 @@
         <v>136</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="N485" t="s" s="2">
         <v>1044</v>
@@ -57627,7 +57630,7 @@
         <v>497</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="N493" t="s" s="2">
         <v>1057</v>
@@ -57833,7 +57836,7 @@
         <v>1059</v>
       </c>
       <c r="M495" t="s" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="N495" t="s" s="2">
         <v>1064</v>
@@ -57936,10 +57939,10 @@
         <v>1066</v>
       </c>
       <c r="M496" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="N496" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="O496" t="s" s="2">
         <v>1069</v>
@@ -58043,10 +58046,10 @@
         <v>130</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="O497" t="s" s="2">
         <v>1074</v>
@@ -58148,7 +58151,7 @@
         <v>497</v>
       </c>
       <c r="M498" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N498" t="s" s="2">
         <v>1077</v>
@@ -58356,7 +58359,7 @@
         <v>670</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="N500" t="s" s="2">
         <v>1093</v>
@@ -58459,7 +58462,7 @@
         <v>136</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="N501" t="s" s="2">
         <v>1096</v>
@@ -59085,7 +59088,7 @@
         <v>819</v>
       </c>
       <c r="M507" t="s" s="2">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="N507" t="s" s="2">
         <v>1111</v>
@@ -59188,7 +59191,7 @@
         <v>886</v>
       </c>
       <c r="M508" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="N508" t="s" s="2">
         <v>1114</v>
@@ -59293,7 +59296,7 @@
         <v>891</v>
       </c>
       <c r="M509" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="N509" t="s" s="2">
         <v>1117</v>
@@ -59366,13 +59369,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -59398,10 +59401,10 @@
         <v>78</v>
       </c>
       <c r="M510" t="s" s="2">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="O510" s="2"/>
       <c r="P510" s="2"/>
@@ -59452,7 +59455,7 @@
         <v>23</v>
       </c>
       <c r="AG510" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="AH510" t="s" s="2">
         <v>76</v>
@@ -59469,13 +59472,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59574,13 +59577,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -59677,13 +59680,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -59782,13 +59785,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -59887,13 +59890,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -59992,13 +59995,13 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -60097,13 +60100,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -60202,13 +60205,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -60309,13 +60312,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -60341,13 +60344,13 @@
         <v>112</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="N519" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="O519" t="s" s="2">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="P519" s="2"/>
       <c r="Q519" t="s" s="2">
@@ -60397,7 +60400,7 @@
         <v>23</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>76</v>
@@ -60414,13 +60417,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60446,10 +60449,10 @@
         <v>103</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="N520" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="O520" s="2"/>
       <c r="P520" s="2"/>
@@ -60479,10 +60482,10 @@
         <v>121</v>
       </c>
       <c r="Z520" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="AA520" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="AB520" t="s" s="2">
         <v>23</v>
@@ -60500,7 +60503,7 @@
         <v>23</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>76</v>
@@ -60517,13 +60520,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -60549,13 +60552,13 @@
         <v>367</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="O521" t="s" s="2">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="P521" s="2"/>
       <c r="Q521" t="s" s="2">
@@ -60581,13 +60584,13 @@
         <v>23</v>
       </c>
       <c r="Y521" t="s" s="2">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="Z521" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="AA521" t="s" s="2">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="AB521" t="s" s="2">
         <v>23</v>
@@ -60605,7 +60608,7 @@
         <v>23</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>76</v>
@@ -60622,13 +60625,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -60654,13 +60657,13 @@
         <v>367</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="N522" t="s" s="2">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="O522" t="s" s="2">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="P522" s="2"/>
       <c r="Q522" t="s" s="2">
@@ -60689,10 +60692,10 @@
         <v>372</v>
       </c>
       <c r="Z522" t="s" s="2">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="AA522" t="s" s="2">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="AB522" t="s" s="2">
         <v>23</v>
@@ -60710,7 +60713,7 @@
         <v>23</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>83</v>
@@ -60727,13 +60730,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -60759,10 +60762,10 @@
         <v>141</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="N523" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="O523" s="2"/>
       <c r="P523" s="2"/>
@@ -60813,7 +60816,7 @@
         <v>23</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>76</v>
@@ -60830,13 +60833,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -60862,10 +60865,10 @@
         <v>136</v>
       </c>
       <c r="M524" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="N524" t="s" s="2">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="O524" s="2"/>
       <c r="P524" s="2"/>
@@ -60873,7 +60876,7 @@
         <v>23</v>
       </c>
       <c r="R524" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="S524" t="s" s="2">
         <v>23</v>
@@ -60918,7 +60921,7 @@
         <v>23</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="AH524" t="s" s="2">
         <v>76</v>
@@ -60935,13 +60938,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -61038,13 +61041,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -61143,13 +61146,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -61250,13 +61253,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -61282,10 +61285,10 @@
         <v>112</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="O528" s="2"/>
       <c r="P528" s="2"/>
@@ -61336,7 +61339,7 @@
         <v>23</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>76</v>
@@ -61353,13 +61356,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -61385,10 +61388,10 @@
         <v>578</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="N529" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="O529" s="2"/>
       <c r="P529" s="2"/>
@@ -61439,7 +61442,7 @@
         <v>23</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>76</v>
@@ -61456,13 +61459,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -61488,10 +61491,10 @@
         <v>497</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="O530" s="2"/>
       <c r="P530" s="2"/>
@@ -61542,7 +61545,7 @@
         <v>23</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>76</v>
@@ -61559,13 +61562,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -61591,10 +61594,10 @@
         <v>136</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="O531" s="2"/>
       <c r="P531" s="2"/>
@@ -61645,7 +61648,7 @@
         <v>23</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>76</v>
@@ -61662,13 +61665,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -61765,13 +61768,13 @@
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -61870,13 +61873,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -61977,13 +61980,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
@@ -62009,10 +62012,10 @@
         <v>491</v>
       </c>
       <c r="M535" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="N535" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="O535" s="2"/>
       <c r="P535" s="2"/>
@@ -62063,7 +62066,7 @@
         <v>23</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>76</v>
@@ -62080,13 +62083,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -62109,13 +62112,13 @@
         <v>84</v>
       </c>
       <c r="L536" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="N536" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="O536" s="2"/>
       <c r="P536" s="2"/>
@@ -62145,10 +62148,10 @@
         <v>372</v>
       </c>
       <c r="Z536" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="AA536" t="s" s="2">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="AB536" t="s" s="2">
         <v>23</v>
@@ -62166,7 +62169,7 @@
         <v>23</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>83</v>
@@ -62183,13 +62186,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -62215,13 +62218,13 @@
         <v>78</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="N537" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="O537" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="P537" s="2"/>
       <c r="Q537" t="s" s="2">
@@ -62271,7 +62274,7 @@
         <v>23</v>
       </c>
       <c r="AG537" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="AH537" t="s" s="2">
         <v>76</v>
@@ -62288,13 +62291,13 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -62391,13 +62394,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62496,13 +62499,13 @@
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -62603,13 +62606,13 @@
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -62635,14 +62638,14 @@
         <v>578</v>
       </c>
       <c r="M541" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="N541" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="O541" s="2"/>
       <c r="P541" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="Q541" t="s" s="2">
         <v>23</v>
@@ -62691,7 +62694,7 @@
         <v>23</v>
       </c>
       <c r="AG541" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="AH541" t="s" s="2">
         <v>76</v>
@@ -62708,13 +62711,13 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
@@ -62740,14 +62743,14 @@
         <v>418</v>
       </c>
       <c r="M542" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="N542" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="O542" s="2"/>
       <c r="P542" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="Q542" t="s" s="2">
         <v>23</v>
@@ -62796,7 +62799,7 @@
         <v>23</v>
       </c>
       <c r="AG542" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="AH542" t="s" s="2">
         <v>76</v>
@@ -62808,18 +62811,18 @@
         <v>23</v>
       </c>
       <c r="AK542" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
@@ -62916,13 +62919,13 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
@@ -63021,13 +63024,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -63050,13 +63053,13 @@
         <v>84</v>
       </c>
       <c r="L545" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="M545" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="N545" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="O545" s="2"/>
       <c r="P545" s="2"/>
@@ -63105,7 +63108,7 @@
         <v>355</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>76</v>
@@ -63122,16 +63125,16 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="D546" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="E546" t="s" s="2">
         <v>23</v>
@@ -63156,10 +63159,10 @@
         <v>1066</v>
       </c>
       <c r="M546" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="N546" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="O546" s="2"/>
       <c r="P546" s="2"/>
@@ -63210,7 +63213,7 @@
         <v>23</v>
       </c>
       <c r="AG546" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="AH546" t="s" s="2">
         <v>76</v>
@@ -63227,13 +63230,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63330,13 +63333,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -63435,13 +63438,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -63467,13 +63470,13 @@
         <v>578</v>
       </c>
       <c r="M549" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="N549" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="O549" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="P549" s="2"/>
       <c r="Q549" t="s" s="2">
@@ -63523,7 +63526,7 @@
         <v>23</v>
       </c>
       <c r="AG549" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="AH549" t="s" s="2">
         <v>76</v>
@@ -63532,7 +63535,7 @@
         <v>83</v>
       </c>
       <c r="AJ549" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="AK549" t="s" s="2">
         <v>95</v>
@@ -63540,13 +63543,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -63572,20 +63575,20 @@
         <v>578</v>
       </c>
       <c r="M550" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="N550" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="O550" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="P550" s="2"/>
       <c r="Q550" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R550" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="S550" t="s" s="2">
         <v>23</v>
@@ -63630,7 +63633,7 @@
         <v>23</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>76</v>
@@ -63639,7 +63642,7 @@
         <v>83</v>
       </c>
       <c r="AJ550" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="AK550" t="s" s="2">
         <v>95</v>
@@ -63647,13 +63650,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -63676,19 +63679,19 @@
         <v>84</v>
       </c>
       <c r="L551" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="M551" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="N551" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="O551" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="P551" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="Q551" t="s" s="2">
         <v>23</v>
@@ -63737,7 +63740,7 @@
         <v>23</v>
       </c>
       <c r="AG551" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="AH551" t="s" s="2">
         <v>76</v>
@@ -63754,13 +63757,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -63783,13 +63786,13 @@
         <v>84</v>
       </c>
       <c r="L552" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="M552" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="N552" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="O552" s="2"/>
       <c r="P552" s="2"/>
@@ -63840,7 +63843,7 @@
         <v>23</v>
       </c>
       <c r="AG552" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="AH552" t="s" s="2">
         <v>76</v>
@@ -63857,13 +63860,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -63889,16 +63892,16 @@
         <v>199</v>
       </c>
       <c r="M553" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="N553" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="O553" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="P553" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="Q553" t="s" s="2">
         <v>23</v>
@@ -63947,7 +63950,7 @@
         <v>23</v>
       </c>
       <c r="AG553" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="AH553" t="s" s="2">
         <v>76</v>
@@ -63964,13 +63967,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -63996,16 +63999,16 @@
         <v>199</v>
       </c>
       <c r="M554" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="N554" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="O554" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="P554" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="Q554" t="s" s="2">
         <v>23</v>
@@ -64054,7 +64057,7 @@
         <v>23</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>76</v>
@@ -64071,13 +64074,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -64103,10 +64106,10 @@
         <v>103</v>
       </c>
       <c r="M555" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="N555" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
@@ -64136,10 +64139,10 @@
         <v>121</v>
       </c>
       <c r="Z555" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="AA555" t="s" s="2">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="AB555" t="s" s="2">
         <v>23</v>
@@ -64157,7 +64160,7 @@
         <v>23</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>76</v>
@@ -64174,13 +64177,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -64203,13 +64206,13 @@
         <v>84</v>
       </c>
       <c r="L556" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="M556" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="N556" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="O556" s="2"/>
       <c r="P556" s="2"/>
@@ -64217,7 +64220,7 @@
         <v>23</v>
       </c>
       <c r="R556" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="S556" t="s" s="2">
         <v>23</v>
@@ -64262,7 +64265,7 @@
         <v>23</v>
       </c>
       <c r="AG556" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="AH556" t="s" s="2">
         <v>76</v>
@@ -64279,13 +64282,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -64308,13 +64311,13 @@
         <v>84</v>
       </c>
       <c r="L557" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="M557" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="N557" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
@@ -64365,7 +64368,7 @@
         <v>23</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>76</v>
@@ -64382,13 +64385,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -64414,10 +64417,10 @@
         <v>199</v>
       </c>
       <c r="M558" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="N558" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="O558" s="2"/>
       <c r="P558" s="2"/>
@@ -64468,7 +64471,7 @@
         <v>23</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>76</v>
@@ -64485,13 +64488,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -64517,10 +64520,10 @@
         <v>199</v>
       </c>
       <c r="M559" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="N559" t="s" s="2">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="O559" s="2"/>
       <c r="P559" s="2"/>
@@ -64571,7 +64574,7 @@
         <v>23</v>
       </c>
       <c r="AG559" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="AH559" t="s" s="2">
         <v>76</v>
@@ -64588,13 +64591,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -64620,10 +64623,10 @@
         <v>103</v>
       </c>
       <c r="M560" t="s" s="2">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="N560" t="s" s="2">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="O560" s="2"/>
       <c r="P560" s="2"/>
@@ -64654,7 +64657,7 @@
       </c>
       <c r="Z560" s="2"/>
       <c r="AA560" t="s" s="2">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="AB560" t="s" s="2">
         <v>23</v>
@@ -64672,7 +64675,7 @@
         <v>23</v>
       </c>
       <c r="AG560" t="s" s="2">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="AH560" t="s" s="2">
         <v>76</v>
@@ -64689,13 +64692,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -64721,13 +64724,13 @@
         <v>103</v>
       </c>
       <c r="M561" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="N561" t="s" s="2">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="O561" t="s" s="2">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="P561" s="2"/>
       <c r="Q561" t="s" s="2">
@@ -64757,7 +64760,7 @@
       </c>
       <c r="Z561" s="2"/>
       <c r="AA561" t="s" s="2">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="AB561" t="s" s="2">
         <v>23</v>
@@ -64775,7 +64778,7 @@
         <v>23</v>
       </c>
       <c r="AG561" t="s" s="2">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="AH561" t="s" s="2">
         <v>76</v>
@@ -64792,13 +64795,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -64821,16 +64824,16 @@
         <v>84</v>
       </c>
       <c r="L562" t="s" s="2">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="M562" t="s" s="2">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="N562" t="s" s="2">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="O562" t="s" s="2">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="P562" s="2"/>
       <c r="Q562" t="s" s="2">
@@ -64880,7 +64883,7 @@
         <v>23</v>
       </c>
       <c r="AG562" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="AH562" t="s" s="2">
         <v>76</v>
@@ -64897,13 +64900,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -64929,16 +64932,16 @@
         <v>103</v>
       </c>
       <c r="M563" t="s" s="2">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="N563" t="s" s="2">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="O563" t="s" s="2">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="P563" t="s" s="2">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="Q563" t="s" s="2">
         <v>23</v>
@@ -64967,7 +64970,7 @@
       </c>
       <c r="Z563" s="2"/>
       <c r="AA563" t="s" s="2">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="AB563" t="s" s="2">
         <v>23</v>
@@ -64985,7 +64988,7 @@
         <v>23</v>
       </c>
       <c r="AG563" t="s" s="2">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="AH563" t="s" s="2">
         <v>76</v>
@@ -65002,13 +65005,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="D564" s="2"/>
       <c r="E564" t="s" s="2">
@@ -65034,10 +65037,10 @@
         <v>130</v>
       </c>
       <c r="M564" t="s" s="2">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="N564" t="s" s="2">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="O564" s="2"/>
       <c r="P564" s="2"/>
@@ -65088,7 +65091,7 @@
         <v>23</v>
       </c>
       <c r="AG564" t="s" s="2">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="AH564" t="s" s="2">
         <v>76</v>
@@ -65105,13 +65108,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D565" s="2"/>
       <c r="E565" t="s" s="2">
@@ -65137,13 +65140,13 @@
         <v>367</v>
       </c>
       <c r="M565" t="s" s="2">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="N565" t="s" s="2">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="O565" t="s" s="2">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="P565" s="2"/>
       <c r="Q565" t="s" s="2">
@@ -65172,10 +65175,10 @@
         <v>107</v>
       </c>
       <c r="Z565" t="s" s="2">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="AA565" t="s" s="2">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="AB565" t="s" s="2">
         <v>23</v>
@@ -65193,7 +65196,7 @@
         <v>23</v>
       </c>
       <c r="AG565" t="s" s="2">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="AH565" t="s" s="2">
         <v>76</v>

--- a/r4-ELGA-e-Medikation-uc_5_6/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-uc_5_6/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:07:25+00:00</t>
+    <t>2026-07-16T16:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
